--- a/project_summary.xlsx
+++ b/project_summary.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Python\project_file_system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A637DFD4-BD07-46BB-BC87-F25AF52576FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1338A89C-98DB-494C-A264-ACAB16EC01EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10608" yWindow="2244" windowWidth="22296" windowHeight="13236" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15360" yWindow="0" windowWidth="15360" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="755">
   <si>
     <t>RFFM-1001-A</t>
   </si>
@@ -2300,6 +2311,18 @@
   </si>
   <si>
     <t>customer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RFFM-1520-LC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DPM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常规白光照明，出线方向与散热器出风方向同向</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2637,7 +2660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E414"/>
+  <dimension ref="A1:E415"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="30.33203125" style="1" customWidth="1"/>
@@ -4673,88 +4696,91 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C155" s="2">
+        <v>45925</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C155" s="2">
+      <c r="C156" s="2">
         <v>45624</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C156" s="2">
-        <v>42928</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>165</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C157" s="2">
-        <v>44428</v>
+        <v>42928</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>165</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>639</v>
+        <v>708</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C158" s="2">
-        <v>44433</v>
+        <v>44428</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>165</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>709</v>
+        <v>639</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C159" s="2">
-        <v>45068</v>
+        <v>44433</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>165</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>695</v>
+        <v>709</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C160" s="2">
-        <v>44260</v>
+        <v>45068</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>165</v>
       </c>
+      <c r="E160" s="1" t="s">
+        <v>695</v>
+      </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C161" s="2">
         <v>44260</v>
@@ -4762,27 +4788,24 @@
       <c r="D161" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E161" s="1" t="s">
-        <v>695</v>
-      </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C162" s="2">
-        <v>44431</v>
+        <v>44260</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>165</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C163" s="2">
         <v>44431</v>
@@ -4791,45 +4814,45 @@
         <v>165</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
+      </c>
+      <c r="C164" s="2">
+        <v>44431</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>207</v>
+        <v>165</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C165" s="2">
-        <v>43763</v>
+        <v>206</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C166" s="2">
-        <v>44277</v>
+        <v>43763</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>711</v>
+        <v>209</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C167" s="2">
         <v>44277</v>
@@ -4843,7 +4866,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C168" s="2">
         <v>44277</v>
@@ -4857,256 +4880,256 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C169" s="2">
-        <v>45419</v>
+        <v>44277</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>645</v>
+        <v>711</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C170" s="2">
-        <v>45743</v>
+        <v>45419</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>712</v>
+        <v>645</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C171" s="2">
-        <v>43244</v>
+        <v>45743</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>675</v>
+        <v>712</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
+      </c>
+      <c r="C172" s="2">
+        <v>43244</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>630</v>
+        <v>675</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>209</v>
       </c>
+      <c r="E173" s="1" t="s">
+        <v>630</v>
+      </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C174" s="2">
-        <v>44088</v>
+        <v>221</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E174" s="1" t="s">
-        <v>713</v>
-      </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C175" s="2">
-        <v>44286</v>
+        <v>44088</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>209</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>662</v>
+        <v>713</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C176" s="2">
-        <v>44343</v>
+        <v>44286</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>209</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>698</v>
+        <v>662</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C177" s="2">
-        <v>44364</v>
+        <v>44343</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>209</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>665</v>
+        <v>698</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C178" s="2">
-        <v>44378</v>
+        <v>44364</v>
       </c>
       <c r="D178" s="3" t="s">
         <v>209</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>714</v>
+        <v>665</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C179" s="2">
-        <v>44445</v>
+        <v>44378</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>209</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>693</v>
+        <v>714</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C180" s="2">
-        <v>44531</v>
+        <v>44445</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>679</v>
+        <v>693</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C181" s="2">
-        <v>44552</v>
+        <v>44531</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>715</v>
+        <v>679</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C182" s="2">
-        <v>44692</v>
+        <v>44552</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>209</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>641</v>
+        <v>715</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>620</v>
+        <v>230</v>
       </c>
       <c r="C183" s="2">
-        <v>44364</v>
+        <v>44692</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>9</v>
+        <v>209</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>665</v>
+        <v>641</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>231</v>
+        <v>615</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>620</v>
       </c>
       <c r="C184" s="2">
-        <v>44810</v>
+        <v>44364</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>219</v>
+        <v>9</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>630</v>
+        <v>665</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C185" s="2">
-        <v>44887</v>
+        <v>44810</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>662</v>
+        <v>630</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C186" s="2">
-        <v>44894</v>
+        <v>44887</v>
       </c>
       <c r="D186" s="3" t="s">
         <v>209</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>713</v>
+        <v>662</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C187" s="2">
-        <v>45061</v>
+        <v>44894</v>
       </c>
       <c r="D187" s="3" t="s">
         <v>209</v>
@@ -5117,74 +5140,74 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C188" s="2">
-        <v>45768</v>
+        <v>45061</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>713</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C189" s="2">
-        <v>45188</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>665</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C190" s="2">
-        <v>44557</v>
+        <v>45188</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>238</v>
+        <v>29</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C191" s="2">
-        <v>45121</v>
+        <v>44557</v>
       </c>
       <c r="D191" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E191" s="1" t="s">
-        <v>675</v>
-      </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C192" s="2">
-        <v>45420</v>
+        <v>45121</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>713</v>
+        <v>675</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C193" s="2">
-        <v>45428</v>
+        <v>45420</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>713</v>
@@ -5192,247 +5215,253 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C194" s="2">
-        <v>45408</v>
+        <v>45428</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>671</v>
+        <v>713</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C195" s="2">
-        <v>45461</v>
+        <v>45408</v>
       </c>
       <c r="D195" s="3" t="s">
         <v>209</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>707</v>
+        <v>671</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C196" s="2">
-        <v>45603</v>
+        <v>45461</v>
       </c>
       <c r="D196" s="3" t="s">
         <v>209</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>630</v>
+        <v>707</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C197" s="2">
-        <v>45730</v>
+        <v>45603</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>209</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>716</v>
+        <v>630</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C198" s="2">
-        <v>45309</v>
+        <v>45730</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C199" s="2">
-        <v>45145</v>
+        <v>45309</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>217</v>
       </c>
+      <c r="E199" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C200" s="2">
-        <v>45377</v>
+        <v>45145</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E200" s="1" t="s">
-        <v>712</v>
-      </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C201" s="2">
-        <v>45492</v>
+        <v>45377</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C202" s="2">
-        <v>44389</v>
+        <v>45492</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>689</v>
+        <v>718</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C203" s="2">
         <v>44389</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>716</v>
+        <v>689</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C204" s="2">
-        <v>45042</v>
+        <v>44389</v>
       </c>
       <c r="D204" s="3" t="s">
         <v>255</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C205" s="2">
-        <v>45384</v>
+        <v>45042</v>
       </c>
       <c r="D205" s="3" t="s">
         <v>255</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>640</v>
+        <v>719</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C206" s="2">
-        <v>45009</v>
+        <v>45384</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>662</v>
+        <v>640</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C207" s="2">
-        <v>45546</v>
+        <v>45009</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>702</v>
+        <v>662</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C208" s="2">
-        <v>45622</v>
+        <v>45546</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>675</v>
+        <v>702</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C209" s="2">
-        <v>43627</v>
+        <v>45622</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C210" s="2">
-        <v>43431</v>
+        <v>43627</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>688</v>
+        <v>265</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
+      </c>
+      <c r="C211" s="2">
+        <v>43431</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>268</v>
+        <v>209</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D212" s="3" t="s">
         <v>268</v>
@@ -5440,380 +5469,380 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C213" s="2">
-        <v>44133</v>
+        <v>269</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>720</v>
+        <v>268</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C214" s="2">
-        <v>44434</v>
+        <v>44133</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C215" s="2">
-        <v>44490</v>
+        <v>44434</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>268</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>692</v>
+        <v>721</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C216" s="2">
-        <v>44559</v>
+        <v>44490</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C217" s="2">
-        <v>44722</v>
+        <v>44559</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C218" s="2">
-        <v>44750</v>
+        <v>44722</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>268</v>
       </c>
+      <c r="E218" s="1" t="s">
+        <v>702</v>
+      </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C219" s="2">
-        <v>44756</v>
+        <v>44750</v>
       </c>
       <c r="D219" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="E219" s="1" t="s">
-        <v>671</v>
-      </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C220" s="2">
-        <v>44874</v>
+        <v>44756</v>
       </c>
       <c r="D220" s="3" t="s">
         <v>268</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C221" s="2">
-        <v>44932</v>
+        <v>44874</v>
       </c>
       <c r="D221" s="3" t="s">
         <v>268</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>705</v>
+        <v>689</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C222" s="2">
-        <v>45009</v>
+        <v>44932</v>
       </c>
       <c r="D222" s="3" t="s">
         <v>268</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C223" s="2">
-        <v>45070</v>
+        <v>45009</v>
       </c>
       <c r="D223" s="3" t="s">
         <v>268</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>671</v>
+        <v>702</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C224" s="2">
-        <v>45107</v>
+        <v>45070</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>268</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>722</v>
+        <v>671</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C225" s="2">
-        <v>44988</v>
+        <v>45107</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>238</v>
+        <v>268</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C226" s="2">
-        <v>44645</v>
+        <v>44988</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E226" s="1" t="s">
-        <v>723</v>
+        <v>238</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C227" s="2">
-        <v>44999</v>
+        <v>44645</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>689</v>
+        <v>723</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C228" s="2">
-        <v>45161</v>
+        <v>44999</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>286</v>
       </c>
+      <c r="E228" s="1" t="s">
+        <v>689</v>
+      </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C229" s="2">
-        <v>45191</v>
+        <v>45161</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E229" s="1" t="s">
-        <v>724</v>
+        <v>286</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C230" s="2">
-        <v>45169</v>
+        <v>45191</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>209</v>
+        <v>289</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C231" s="2">
-        <v>45776</v>
+        <v>45169</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>209</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>682</v>
+        <v>725</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C232" s="2">
-        <v>45875</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>209</v>
+        <v>45776</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>726</v>
+        <v>682</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C233" s="2">
-        <v>43572</v>
+        <v>45875</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>294</v>
+        <v>209</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>726</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C234" s="2">
-        <v>43726</v>
+        <v>43572</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E234" s="1" t="s">
-        <v>727</v>
+        <v>294</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C235" s="2">
-        <v>42996</v>
+        <v>43726</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>653</v>
+        <v>727</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C236" s="2">
-        <v>44546</v>
+        <v>42996</v>
       </c>
       <c r="D236" s="3" t="s">
         <v>298</v>
       </c>
+      <c r="E236" s="1" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C237" s="2">
-        <v>45112</v>
+        <v>44546</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E237" s="1" t="s">
-        <v>669</v>
+        <v>298</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
+      </c>
+      <c r="C238" s="2">
+        <v>45112</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C239" s="2">
-        <v>43902</v>
+        <v>302</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E239" s="1" t="s">
-        <v>695</v>
+        <v>303</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C240" s="2">
-        <v>43801</v>
+        <v>43902</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
+      </c>
+      <c r="C241" s="2">
+        <v>43801</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D242" s="3" t="s">
         <v>309</v>
@@ -5821,65 +5850,62 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="C243" s="2">
-        <v>43934</v>
+        <v>310</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="E243" s="1" t="s">
-        <v>728</v>
+        <v>309</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
+      </c>
+      <c r="C244" s="2">
+        <v>43934</v>
       </c>
       <c r="D244" s="3" t="s">
         <v>312</v>
       </c>
+      <c r="E244" s="1" t="s">
+        <v>728</v>
+      </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C245" s="2">
-        <v>44167</v>
+        <v>313</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
+      </c>
+      <c r="C246" s="2">
+        <v>44167</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="E246" s="1" t="s">
-        <v>729</v>
+        <v>303</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>681</v>
+        <v>729</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>681</v>
@@ -5887,183 +5913,183 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C249" s="2">
-        <v>45212</v>
+        <v>319</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C250" s="2">
-        <v>45012</v>
+        <v>45212</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>730</v>
+        <v>695</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C251" s="2">
-        <v>45085</v>
+        <v>45012</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>645</v>
+        <v>730</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C252" s="2">
-        <v>44818</v>
+        <v>45085</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>664</v>
+        <v>645</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C253" s="2">
-        <v>44805</v>
+        <v>44818</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>731</v>
+        <v>664</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C254" s="2">
-        <v>45768</v>
+        <v>44805</v>
       </c>
       <c r="D254" s="3" t="s">
         <v>309</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>645</v>
+        <v>731</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C255" s="2">
-        <v>44843</v>
+        <v>45768</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>331</v>
+        <v>309</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C256" s="2">
-        <v>44886</v>
+        <v>44843</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C257" s="2">
-        <v>45512</v>
+        <v>44886</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="E257" s="1" t="s">
-        <v>730</v>
+        <v>303</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C258" s="2">
-        <v>45776</v>
+        <v>45512</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>662</v>
+        <v>730</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C259" s="2">
-        <v>45623</v>
+        <v>45776</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>648</v>
+        <v>662</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C260" s="2">
-        <v>45650</v>
+        <v>45623</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C261" s="2">
-        <v>45105</v>
+        <v>45650</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C262" s="2">
-        <v>45317</v>
+        <v>45105</v>
       </c>
       <c r="D262" s="3" t="s">
         <v>341</v>
@@ -6071,10 +6097,10 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C263" s="2">
-        <v>45826</v>
+        <v>45317</v>
       </c>
       <c r="D263" s="3" t="s">
         <v>341</v>
@@ -6082,143 +6108,140 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C264" s="2">
-        <v>45423</v>
+        <v>45826</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C265" s="2">
         <v>45423</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="E265" s="1" t="s">
-        <v>732</v>
+        <v>345</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C266" s="2">
-        <v>45477</v>
+        <v>45423</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>689</v>
+        <v>732</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
+      </c>
+      <c r="C267" s="2">
+        <v>45477</v>
       </c>
       <c r="D267" s="3" t="s">
         <v>349</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>630</v>
+        <v>689</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C268" s="2">
-        <v>45774</v>
+        <v>350</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>655</v>
+        <v>630</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C269" s="2">
-        <v>45729</v>
+        <v>45774</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C270" s="2">
-        <v>45455</v>
-      </c>
-      <c r="D270" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="E270" s="1" t="s">
-        <v>733</v>
+        <v>45729</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C271" s="2">
-        <v>45189</v>
+        <v>45455</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C272" s="2">
-        <v>45288</v>
-      </c>
-      <c r="D272" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="E272" s="1" t="s">
-        <v>650</v>
+        <v>45189</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
+      </c>
+      <c r="C273" s="2">
+        <v>45288</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C274" s="2">
-        <v>45758</v>
+        <v>358</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="E274" s="1" t="s">
-        <v>650</v>
+        <v>359</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C275" s="2">
-        <v>45484</v>
+        <v>45758</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>650</v>
@@ -6226,96 +6249,93 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C276" s="2">
-        <v>45917</v>
+        <v>45484</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>734</v>
+        <v>650</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C277" s="2">
-        <v>45575</v>
+        <v>45917</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>630</v>
+        <v>734</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C278" s="2">
-        <v>45698</v>
+        <v>45575</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C279" s="2">
-        <v>45866</v>
+        <v>45698</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="E279" s="1" t="s">
-        <v>734</v>
+        <v>368</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
+      </c>
+      <c r="C280" s="2">
+        <v>45866</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="B282" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="C282" s="2">
-        <v>45595</v>
+        <v>373</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="E282" s="1" t="s">
-        <v>650</v>
+        <v>374</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C283" s="2">
         <v>45595</v>
@@ -6329,10 +6349,13 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>376</v>
+        <v>613</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>622</v>
       </c>
       <c r="C284" s="2">
-        <v>45702</v>
+        <v>45595</v>
       </c>
       <c r="D284" s="3" t="s">
         <v>375</v>
@@ -6343,96 +6366,96 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C285" s="2">
-        <v>45785</v>
+        <v>45702</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C286" s="2">
-        <v>45806</v>
+        <v>45785</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C287" s="2">
-        <v>43224</v>
+        <v>45806</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="E287" s="1" t="s">
-        <v>698</v>
+        <v>380</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C288" s="2">
-        <v>44645</v>
+        <v>43224</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C289" s="2">
-        <v>42894</v>
+        <v>44645</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="E289" s="1" t="s">
-        <v>630</v>
+        <v>384</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C290" s="2">
-        <v>43105</v>
+        <v>42894</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
+      </c>
+      <c r="C291" s="2">
+        <v>43105</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="E291" s="1" t="s">
-        <v>735</v>
+        <v>388</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="C292" s="2">
-        <v>43308</v>
+        <v>389</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>735</v>
@@ -6440,13 +6463,13 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C293" s="2">
         <v>43308</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>735</v>
@@ -6454,57 +6477,57 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C294" s="2">
-        <v>43474</v>
+        <v>43308</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C295" s="2">
-        <v>43772</v>
+        <v>43474</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C296" s="2">
-        <v>44382</v>
+        <v>43772</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C297" s="2">
-        <v>45124</v>
-      </c>
-      <c r="D297" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E297" s="1" t="s">
-        <v>737</v>
+        <v>44382</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C298" s="2">
-        <v>45806</v>
+        <v>45124</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>737</v>
@@ -6512,38 +6535,41 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C299" s="2">
-        <v>43880</v>
+        <v>45806</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>653</v>
+        <v>737</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C300" s="2">
-        <v>43117</v>
+        <v>43880</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>630</v>
+        <v>653</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
+      </c>
+      <c r="C301" s="2">
+        <v>43117</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>630</v>
@@ -6551,13 +6577,10 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C302" s="2">
-        <v>44525</v>
+        <v>407</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>630</v>
@@ -6565,13 +6588,13 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C303" s="2">
-        <v>43411</v>
+        <v>44525</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>630</v>
@@ -6579,160 +6602,163 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="B304" s="1" t="s">
-        <v>623</v>
+        <v>411</v>
       </c>
       <c r="C304" s="2">
-        <v>45825</v>
+        <v>43411</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>414</v>
+        <v>612</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="C305" s="2">
-        <v>45905</v>
+        <v>45825</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C306" s="2">
-        <v>44608</v>
+        <v>45905</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="E306" s="1" t="s">
-        <v>681</v>
+        <v>415</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C307" s="2">
-        <v>44433</v>
+        <v>44608</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>738</v>
+        <v>681</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C308" s="2">
-        <v>44431</v>
+        <v>44433</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C309" s="2">
         <v>44431</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C310" s="2">
-        <v>45075</v>
+        <v>44431</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
+      </c>
+      <c r="E310" s="1" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
+      </c>
+      <c r="C311" s="2">
+        <v>45075</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="E311" s="1" t="s">
-        <v>730</v>
+        <v>425</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C312" s="2">
-        <v>44588</v>
+        <v>426</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
+      </c>
+      <c r="E312" s="1" t="s">
+        <v>730</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C313" s="2">
-        <v>43936</v>
+        <v>44588</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C314" s="2">
-        <v>44088</v>
+        <v>43936</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="E314" s="1" t="s">
-        <v>741</v>
+        <v>431</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
+      </c>
+      <c r="C315" s="2">
+        <v>44088</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>711</v>
+        <v>741</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>711</v>
@@ -6740,10 +6766,10 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>711</v>
@@ -6751,155 +6777,152 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="C318" s="2">
-        <v>44438</v>
+        <v>438</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>742</v>
+        <v>711</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C319" s="2">
-        <v>45432</v>
+        <v>44438</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
+      </c>
+      <c r="E319" s="1" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C320" s="2">
-        <v>44536</v>
+        <v>45432</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C321" s="2">
-        <v>42685</v>
+        <v>44536</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C322" s="2">
-        <v>44914</v>
+        <v>42685</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D323" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
+      </c>
+      <c r="C323" s="2">
+        <v>44914</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="D327" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="E327" s="1" t="s">
-        <v>711</v>
+        <v>454</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="C328" s="2">
-        <v>45881</v>
+        <v>455</v>
+      </c>
+      <c r="D328" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="E328" s="1" t="s">
+        <v>711</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C329" s="2">
-        <v>45225</v>
-      </c>
-      <c r="D329" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="E329" s="1" t="s">
-        <v>743</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C330" s="2">
-        <v>45545</v>
+        <v>45225</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C331" s="2">
-        <v>44088</v>
+        <v>45545</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C332" s="2">
         <v>44088</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>745</v>
@@ -6907,27 +6930,27 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C333" s="2">
-        <v>45007</v>
+        <v>44088</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C334" s="2">
         <v>45007</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>746</v>
@@ -6935,207 +6958,207 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C335" s="2">
-        <v>44183</v>
+        <v>45007</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
+      </c>
+      <c r="E335" s="1" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C336" s="2">
         <v>44183</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="E336" s="1" t="s">
-        <v>747</v>
+        <v>471</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
+      </c>
+      <c r="C337" s="2">
+        <v>44183</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
+      </c>
+      <c r="E337" s="1" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="C339" s="2">
-        <v>44550</v>
+        <v>476</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="E339" s="1" t="s">
-        <v>748</v>
+        <v>477</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C340" s="2">
-        <v>44405</v>
+        <v>44550</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
+      </c>
+      <c r="E340" s="1" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C341" s="2">
-        <v>45342</v>
+        <v>44405</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C342" s="2">
-        <v>45379</v>
+        <v>45342</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C343" s="2">
-        <v>45419</v>
+        <v>45379</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C344" s="2">
-        <v>45225</v>
+        <v>45419</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C345" s="2">
-        <v>45369</v>
+        <v>45225</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
+      </c>
+      <c r="C346" s="2">
+        <v>45369</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="E351" s="1" t="s">
-        <v>749</v>
+        <v>501</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>749</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="C353" s="2">
-        <v>45371</v>
+        <v>504</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="E353" s="1" t="s">
-        <v>630</v>
+        <v>505</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C354" s="2">
-        <v>45824</v>
+        <v>45371</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>630</v>
@@ -7143,13 +7166,13 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C355" s="2">
-        <v>45168</v>
+        <v>45824</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>630</v>
@@ -7157,13 +7180,13 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
-        <v>624</v>
+        <v>510</v>
       </c>
       <c r="C356" s="2">
-        <v>45274</v>
+        <v>45168</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>630</v>
@@ -7171,10 +7194,13 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
-        <v>513</v>
+        <v>624</v>
+      </c>
+      <c r="C357" s="2">
+        <v>45274</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>630</v>
@@ -7182,10 +7208,10 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>630</v>
@@ -7193,10 +7219,10 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>630</v>
@@ -7204,10 +7230,10 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>630</v>
@@ -7215,10 +7241,10 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>630</v>
@@ -7226,13 +7252,10 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="C362" s="2">
-        <v>44565</v>
+        <v>521</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>630</v>
@@ -7240,10 +7263,10 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C363" s="2">
-        <v>44567</v>
+        <v>44565</v>
       </c>
       <c r="D363" s="3" t="s">
         <v>524</v>
@@ -7254,13 +7277,13 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C364" s="2">
-        <v>44762</v>
+        <v>44567</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>630</v>
@@ -7268,13 +7291,13 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C365" s="2">
-        <v>44893</v>
+        <v>44762</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>630</v>
@@ -7282,13 +7305,13 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C366" s="2">
-        <v>45097</v>
+        <v>44893</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>630</v>
@@ -7296,13 +7319,13 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C367" s="2">
-        <v>45155</v>
+        <v>45097</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>630</v>
@@ -7310,10 +7333,13 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
+      </c>
+      <c r="C368" s="2">
+        <v>45155</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>630</v>
@@ -7321,10 +7347,10 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>630</v>
@@ -7332,10 +7358,10 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>630</v>
@@ -7343,10 +7369,10 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>630</v>
@@ -7354,10 +7380,10 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>630</v>
@@ -7365,10 +7391,10 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>630</v>
@@ -7376,10 +7402,10 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>630</v>
@@ -7387,10 +7413,10 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>630</v>
@@ -7398,10 +7424,10 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>630</v>
@@ -7409,13 +7435,10 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="C377" s="2">
-        <v>45516</v>
+        <v>549</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>630</v>
@@ -7423,10 +7446,13 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
+      </c>
+      <c r="C378" s="2">
+        <v>45516</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>630</v>
@@ -7434,10 +7460,10 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>630</v>
@@ -7445,13 +7471,10 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="C380" s="2">
-        <v>45132</v>
+        <v>554</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>630</v>
@@ -7459,10 +7482,13 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
+      </c>
+      <c r="C381" s="2">
+        <v>45132</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>630</v>
@@ -7470,10 +7496,10 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>630</v>
@@ -7481,10 +7507,10 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>630</v>
@@ -7492,10 +7518,10 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>630</v>
@@ -7503,10 +7529,10 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>630</v>
@@ -7514,13 +7540,10 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="C386" s="2">
-        <v>45441</v>
+        <v>564</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>630</v>
@@ -7528,10 +7551,13 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
+      </c>
+      <c r="C387" s="2">
+        <v>45441</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>630</v>
@@ -7539,10 +7565,10 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>568</v>
+        <v>534</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>630</v>
@@ -7550,10 +7576,10 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>544</v>
+        <v>568</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>630</v>
@@ -7561,10 +7587,10 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>630</v>
@@ -7572,10 +7598,10 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>630</v>
@@ -7583,10 +7609,10 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>630</v>
@@ -7594,13 +7620,10 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="C393" s="2">
-        <v>45063</v>
+        <v>573</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>630</v>
@@ -7608,13 +7631,13 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C394" s="2">
-        <v>45247</v>
+        <v>45063</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>630</v>
@@ -7622,10 +7645,13 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
+      </c>
+      <c r="C395" s="2">
+        <v>45247</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>534</v>
+        <v>572</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>630</v>
@@ -7633,13 +7659,10 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="C396" s="2">
-        <v>44767</v>
+        <v>578</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>580</v>
+        <v>534</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>630</v>
@@ -7647,13 +7670,13 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C397" s="2">
-        <v>45722</v>
+        <v>44767</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>630</v>
@@ -7661,13 +7684,13 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C398" s="2">
-        <v>45824</v>
+        <v>45722</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>544</v>
+        <v>582</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>630</v>
@@ -7675,13 +7698,13 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C399" s="2">
-        <v>45877</v>
+        <v>45824</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>585</v>
+        <v>544</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>630</v>
@@ -7689,10 +7712,13 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
+      </c>
+      <c r="C400" s="2">
+        <v>45877</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>630</v>
@@ -7700,10 +7726,10 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>630</v>
@@ -7711,10 +7737,10 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>630</v>
@@ -7722,10 +7748,10 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>630</v>
@@ -7733,10 +7759,10 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>630</v>
@@ -7744,7 +7770,7 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D405" s="3" t="s">
         <v>591</v>
@@ -7755,10 +7781,10 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>630</v>
@@ -7766,10 +7792,10 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>630</v>
@@ -7777,13 +7803,10 @@
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="C408" s="2">
-        <v>45114</v>
+        <v>598</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>630</v>
@@ -7791,13 +7814,13 @@
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C409" s="2">
-        <v>45389</v>
+        <v>45114</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>630</v>
@@ -7805,13 +7828,13 @@
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C410" s="2">
-        <v>45539</v>
+        <v>45389</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>630</v>
@@ -7819,13 +7842,13 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C411" s="2">
-        <v>45747</v>
+        <v>45539</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>630</v>
@@ -7833,10 +7856,13 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
+      </c>
+      <c r="C412" s="2">
+        <v>45747</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>630</v>
@@ -7844,13 +7870,10 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="C413" s="2">
-        <v>45624</v>
+        <v>606</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>630</v>
@@ -7858,15 +7881,29 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="C414" s="2">
+        <v>45624</v>
+      </c>
+      <c r="D414" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="E414" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A415" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="C414" s="2">
+      <c r="C415" s="2">
         <v>45468</v>
       </c>
-      <c r="D414" s="3" t="s">
+      <c r="D415" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="E414" s="1" t="s">
+      <c r="E415" s="1" t="s">
         <v>750</v>
       </c>
     </row>

--- a/project_summary.xlsx
+++ b/project_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Python\project_file_system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1338A89C-98DB-494C-A264-ACAB16EC01EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B7BB17-931B-4308-A35F-9F0DD70A086F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15360" yWindow="0" windowWidth="15360" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2314,15 +2314,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RFFM-1520-LC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DPM</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>常规白光照明，出线方向与散热器出风方向同向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RFFM-1519-LC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4696,16 +4696,16 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C155" s="2">
         <v>45925</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
